--- a/codigos.xlsx
+++ b/codigos.xlsx
@@ -486,7 +486,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="3">
-        <v>277319</v>
+        <v>384283</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -507,7 +507,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="3">
-        <v>268504</v>
+        <v>377969</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -528,7 +528,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="3">
-        <v>297697</v>
+        <v>344640</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -549,7 +549,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="3">
-        <v>269833</v>
+        <v>287367</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -569,9 +569,7 @@
       <c r="Q5" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
-      <c r="A6" s="3">
-        <v>398706</v>
-      </c>
+      <c r="A6" s="3"/>
       <c r="B6" s="2"/>
       <c r="C6" s="4"/>
       <c r="D6" s="2"/>
@@ -590,9 +588,7 @@
       <c r="Q6" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
-      <c r="A7" s="3">
-        <v>327566</v>
-      </c>
+      <c r="A7" s="3"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="4"/>
@@ -611,9 +607,7 @@
       <c r="Q7" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
-      <c r="A8" s="3">
-        <v>268498</v>
-      </c>
+      <c r="A8" s="3"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -632,9 +626,7 @@
       <c r="Q8" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
-      <c r="A9" s="3">
-        <v>268286</v>
-      </c>
+      <c r="A9" s="3"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -653,9 +645,7 @@
       <c r="Q9" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
-      <c r="A10" s="3">
-        <v>357788</v>
-      </c>
+      <c r="A10" s="3"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -674,9 +664,7 @@
       <c r="Q10" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
-      <c r="A11" s="3">
-        <v>269888</v>
-      </c>
+      <c r="A11" s="3"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -695,9 +683,7 @@
       <c r="Q11" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
-      <c r="A12" s="3">
-        <v>380018</v>
-      </c>
+      <c r="A12" s="3"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -716,9 +702,7 @@
       <c r="Q12" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
-      <c r="A13" s="3">
-        <v>269943</v>
-      </c>
+      <c r="A13" s="3"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -737,9 +721,7 @@
       <c r="Q13" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
-      <c r="A14" s="3">
-        <v>269941</v>
-      </c>
+      <c r="A14" s="3"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -758,9 +740,7 @@
       <c r="Q14" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
-      <c r="A15" s="3">
-        <v>269851</v>
-      </c>
+      <c r="A15" s="3"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -779,9 +759,7 @@
       <c r="Q15" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
-      <c r="A16" s="3">
-        <v>397428</v>
-      </c>
+      <c r="A16" s="3"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -800,9 +778,7 @@
       <c r="Q16" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
-      <c r="A17" s="3">
-        <v>296594</v>
-      </c>
+      <c r="A17" s="3"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -821,9 +797,7 @@
       <c r="Q17" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
-      <c r="A18" s="3">
-        <v>296676</v>
-      </c>
+      <c r="A18" s="3"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -842,9 +816,7 @@
       <c r="Q18" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
-      <c r="A19" s="3">
-        <v>305643</v>
-      </c>
+      <c r="A19" s="3"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -863,9 +835,7 @@
       <c r="Q19" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
-      <c r="A20" s="3">
-        <v>307737</v>
-      </c>
+      <c r="A20" s="3"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
@@ -884,9 +854,7 @@
       <c r="Q20" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
-      <c r="A21" s="3">
-        <v>621237</v>
-      </c>
+      <c r="A21" s="3"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
@@ -905,9 +873,7 @@
       <c r="Q21" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
-      <c r="A22" s="3">
-        <v>622621</v>
-      </c>
+      <c r="A22" s="3"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
@@ -926,9 +892,7 @@
       <c r="Q22" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
-      <c r="A23" s="3">
-        <v>622624</v>
-      </c>
+      <c r="A23" s="3"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
@@ -947,9 +911,7 @@
       <c r="Q23" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
-      <c r="A24" s="3">
-        <v>267311</v>
-      </c>
+      <c r="A24" s="3"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
@@ -968,9 +930,7 @@
       <c r="Q24" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
-      <c r="A25" s="3">
-        <v>267378</v>
-      </c>
+      <c r="A25" s="3"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
@@ -989,9 +949,7 @@
       <c r="Q25" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
-      <c r="A26" s="3">
-        <v>267663</v>
-      </c>
+      <c r="A26" s="3"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
@@ -1010,9 +968,7 @@
       <c r="Q26" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
-      <c r="A27" s="3">
-        <v>268222</v>
-      </c>
+      <c r="A27" s="3"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
@@ -1031,9 +987,7 @@
       <c r="Q27" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
-      <c r="A28" s="3">
-        <v>268236</v>
-      </c>
+      <c r="A28" s="3"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
@@ -1052,9 +1006,7 @@
       <c r="Q28" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
-      <c r="A29" s="3">
-        <v>269846</v>
-      </c>
+      <c r="A29" s="3"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
@@ -1073,9 +1025,7 @@
       <c r="Q29" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
-      <c r="A30" s="3">
-        <v>272341</v>
-      </c>
+      <c r="A30" s="3"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
@@ -1094,9 +1044,7 @@
       <c r="Q30" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
-      <c r="A31" s="3">
-        <v>292345</v>
-      </c>
+      <c r="A31" s="3"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
@@ -1115,9 +1063,7 @@
       <c r="Q31" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
-      <c r="A32" s="3">
-        <v>308885</v>
-      </c>
+      <c r="A32" s="3"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
@@ -1136,9 +1082,7 @@
       <c r="Q32" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
-      <c r="A33" s="3">
-        <v>331555</v>
-      </c>
+      <c r="A33" s="3"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
@@ -1157,9 +1101,7 @@
       <c r="Q33" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
-      <c r="A34" s="3">
-        <v>448699</v>
-      </c>
+      <c r="A34" s="3"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
